--- a/tests/fixtures/formatado.xlsx
+++ b/tests/fixtures/formatado.xlsx
@@ -3131,7 +3131,8 @@
     <col min="13" max="13" width="19.7109375" style="162" customWidth="1"/>
     <col min="14" max="14" width="17.5703125" style="162" customWidth="1"/>
     <col min="15" max="15" width="11.7109375" style="162" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="162"/>
+    <col min="16" max="16" width="9.140625" style="162" hidden="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="162"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16">
@@ -3548,8 +3549,9 @@
       <c r="M9" s="156" t="s">
         <v>26</v>
       </c>
-      <c r="N9" s="214" t="s">
-        <v>27</v>
+      <c r="N9" s="214">
+        <f>1+1</f>
+        <v>2</v>
       </c>
       <c r="O9" s="163">
         <v>46212</v>
@@ -3603,6 +3605,17 @@
       <c r="P10" s="279"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:P10"/>
+  <conditionalFormatting sqref="L2:L10">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="DESEMBARA">
+      <formula>NOT(ISERROR(SEARCH("DESEMBARA",L2)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="H2:H10">
+      <formula1>"RIO,SC,MULTI,MULTIRIO,RO"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
 </worksheet>
 </file>

--- a/tests/fixtures/formatado.xlsx
+++ b/tests/fixtures/formatado.xlsx
@@ -5,7 +5,7 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Exemplo\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{0109A3C7-3B61-48FF-9F19-478B0662E973}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
@@ -3103,10 +3103,10 @@
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="E5" dT="2026-07-13T14:05:01.39" personId="{E95E8EAA-183E-49E9-B800-72A393CDF372}" id="{13F3A532-C9D8-45E9-8F90-14493AB154A2}">
-    <text>valor p/Bruna para conta Jhon</text>
+    <text>comentario de teste</text>
   </threadedComment>
   <threadedComment ref="E12" dT="2026-05-20T14:23:38.31" personId="{E95E8EAA-183E-49E9-B800-72A393CDF372}" id="{59788B5C-0757-4D79-81A5-E1811E487993}">
-    <text>GRUPO M8 DOCUMENTOS</text>
+    <text>comentario de teste</text>
   </threadedComment>
 </ThreadedComments>
 </file>
